--- a/controlpribor_bot/products_catalog.xlsx
+++ b/controlpribor_bot/products_catalog.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mahsulotlar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Katalog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -428,16 +428,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,14 +453,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Kategoriya</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Brend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Toifa</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Narxi</t>
@@ -468,12 +468,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Tavsif</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Rasm URL</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tovar Havolasi</t>
         </is>
       </c>
     </row>
@@ -483,34 +483,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ПИРОМЕТР ИНФРАКРАСНЫЙ FLUKE 568</t>
+          <t>Akfix 705 Tezkor universal yelim va aktivator (100ml + 400ml)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10 000 so'm</t>
+          <t>45 000 so'm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/29/2023-12-29-21-38-31-701803-ddb6387de8ffe41da55f05be32d1951c.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/pirometr-infrakrasniy-fluke-568-930701/</t>
-        </is>
-      </c>
+          <t>MDF, yog'och, plastmassa va rezina uchun tezkor ikki komponentli yelim</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -518,34 +514,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IR-67 Инфракрасный термометр (пирометр)</t>
+          <t>Akfix 805 Ko'p maqsadli professional montaj penasi 850g</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>65 000 so'm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/03/2024-01-03-21-22-53-534917-418ad2bcf113f41bf7537bbda28bff97.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/ir-67-infrakrasniy-termometr-pirometr-932437/</t>
-        </is>
-      </c>
+          <t>Eshik va deraza romlarini montaj qilish, bo'shliqlarni to'ldirish uchun termo-izolyatsion ko'pik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -553,34 +545,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Кельвин Компакт 600 (К46) — ИК-термометр</t>
+          <t>Akfix 100E Universal silikon germetik (oq) 280ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6 525 000 so'm</t>
+          <t>35 000 so'm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/02/2024-02-02-12-01-23-286401-fad8dd6f46759895ca8c19ddf269e562.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/kelvin-kompakt-600-k46-ik-termometr-943991/</t>
-        </is>
-      </c>
+          <t>Oshxona, vanna va oynalar choklarini suvdan himoya qiluvchi elastik germetik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -588,34 +576,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Victor 6056A+ AC/DC — токовые клещи</t>
+          <t>Akfix 960 Penoplast va penopolistirol yopishtiruvchi ko'pik-yelim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>72 000 so'm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/20/2024-10-20-11-01-29-676911-16e5bfb1b3d4a8b6a589bb6880846e73.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/victor-6056a-acdc-tokovie-kleshi-1047851/</t>
-        </is>
-      </c>
+          <t>Fasad va issiqlik izolyatsiyasi plitalarini tez va mustahkam yopishtirish uchun</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -623,34 +607,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Michell S8000 — прецизионный гигрометр с охлаждаемым зеркалом</t>
+          <t>Akfix A40 Universal zang erituvchi va moylovchi sprey 400ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Michell</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>AKFIX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>38 000 so'm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/29/2024-11-29-23-31-36-418915-6de0e2a7ad2e1f5d9e328164f6141ad2.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/michell-s8000-pretsizionniy-gigrometr-s-oxlajdaemim-zerkalom-1063303/</t>
-        </is>
-      </c>
+          <t>Zanglagan murvatlarni bo'shatish, metallni korroziyadan himoyalash va moylash uchun</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -658,34 +638,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DT-355 Клещи электроизмерительные, True RMS</t>
+          <t>Terafix Standard Kafellarga mo'ljallangan quruq yelim 25 kg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>42 000 so'm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/01/2024-01-01-22-00-17-631902-0ffb047bad84684a2d3d25002e0620a5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/dt-355-kleshi-elektroizmeritelnie-true-rms-931927/</t>
-        </is>
-      </c>
+          <t>Oddiy keramik plitkalarni bino ichida pol va devorlarga yopishtirish uchun</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,34 +669,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RIGOL DHO1102— цифровой осциллограф</t>
+          <t>Terafix Super Granit va kafel uchun mustahkamlangan yelim 25 kg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15 000 000 so'm</t>
+          <t>58 000 so'm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/20/2024-01-20-10-37-51-508421-b43710421f7d3b9ebf2d93ddf49180c5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rigol-dho1102-tsifrovoy-ostsillograf-940537/</t>
-        </is>
-      </c>
+          <t>Og'ir plitkalar, kafel va tabiiy toshlar uchun issiqqa va sovuqqa chidamli yelim</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -728,34 +700,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Взрывозащищенный датчик давления ATM/Ex</t>
+          <t>Terafix Fuga Plitka choklarini to'ldiruvchi gips chok aralashmasi (oq) 2 kg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>18 000 so'm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/06/2024-05-06-22-45-30-468613-4ba6ca29e4ec8de53e7414192fd2e338.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/vzrivozashishenniy-datchik-davleniya-atmex-994051/</t>
-        </is>
-      </c>
+          <t>Plitkalar orasidagi 1-6 mm choklarni germetik va chiroyli to'ldirish uchun</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -763,34 +731,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SLS-720F классик (Ду 25 мм) — стационарный ультразвуковой расходомер</t>
+          <t>Terafix Betonkontakt Yopishqoqlikni oshiruvchi gruntovka 14 kg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TERAFIX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>145 000 so'm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/31/2023-12-31-10-41-30-517529-c5a019e8e1c6032a8b67875961317539.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/sls-720f-klassik-du-25-mm-statsionarniy-ultrazvukovoy-rasxodomer-931828/</t>
-        </is>
-      </c>
+          <t>Silliq beton yuzalariga suvoq va kafel yelimining yopishishini ta'minlovchi astar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -798,34 +762,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GDM-8245 — вольтметр универсальный цифровой</t>
+          <t>Tytan Professional 65 Yuqori unumdor montaj penasi 850ml</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7 000 000 so'm</t>
+          <t>75 000 so'm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/16/2024-01-16-20-57-24-460934-8d506e427d6cc2aca0699a8a0ba3ecc3.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/gdm-8245-voltmetr-universalniy-tsifrovoy-938139/</t>
-        </is>
-      </c>
+          <t>Kattalashtirilgan 65 litr hajmli, professional pistoletli poliuretan montaj penasi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -833,34 +793,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Elitech V700 — вакуумный насос</t>
+          <t>Tytan Professional B1 Yong'inga chidamli montaj penasi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>110 000 so'm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/03/2024-11-03-23-30-22-326513-a2097f080f2a4efdc8b08179e4e25bb5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/elitech-v700-vakuumniy-nasos-1052362/</t>
-        </is>
-      </c>
+          <t>Yong'inga chidamlilik klassi B1 bo'lgan, kabellar va kanallar o'tish joylarini germetiklash uchun</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -868,34 +824,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HT108L — мультиметр цифровой</t>
+          <t>Tytan Sanitariya silikon germetik (shaffof) 310ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>42 000 so'm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/14/2024-09-14-10-27-54-964996-85dbca89bab5bd412a10089db7256130.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/ht108l-multimetr-tsifrovoy-1036837/</t>
-        </is>
-      </c>
+          <t>Zamburug' va mog'orga qarshi kuchli himoyali, vanna va dush kabinalari uchun</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -903,34 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ТОКОИЗМЕРИТЕЛЬНЫЙ ДАТЧИК FLUKE 376</t>
+          <t>Tytan Classic Fix Sintetik kauchuk asosidagi montaj kleyi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TYTAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>48 000 so'm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/17/2024-09-17-15-46-43-441306-ec99a83afc87c79d0ca8b1f26becb2f4.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/tokoizmeritelniy-datchik-fluke-376-1037935/</t>
-        </is>
-      </c>
+          <t>Plintuslar, yog'och, metall va PVX panellarni mixsiz mustahkam mahkamlash uchun</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -938,34 +886,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PD194PQ-7R0T-A-0001 — многофункциональный цифровой электроизмерительный прибор</t>
+          <t>TESS 1-klavishli o'chirgich (oq) montajli</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>18 000 so'm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/23/2024-04-23-13-19-10-433871-ccf4e9bc939a1504a9236045ad28af6d.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/pd194pq-7r0t-a-0001-mnogofunktsionalniy-tsifrovoy-elektroizmeritelniy-pribor-967633/</t>
-        </is>
-      </c>
+          <t>Zamonaviy dizayn, kumush kontaktli ishonchli mexanizm, 250V 10A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -973,34 +917,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNI-T UT383BT — измеритель освещенности (люксметр) mini</t>
+          <t>TESS 2-klavishli o'chirgich (oq) montajli</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNI-T</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>22 000 so'm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/22/2024-11-22-19-35-23-500110-a7d81776762b26bdb2912c649630eb7a.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/uni-t-ut383bt-izmeritel-osveshennosti-lyuksmetr-mini-1060271/</t>
-        </is>
-      </c>
+          <t>Ikki zanjirli yoritish tizimlari uchun qulay kalit, 250V 10A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1008,34 +948,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MSO5072 — цифровой осциллограф</t>
+          <t>TESS Yerga ulangan rozetka (oq) pardali</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>21 000 so'm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-22-48-46-424996-d51a58237e369e1923aa448a4ec26264.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/mso5072-tsifrovoy-ostsillograf-1060721/</t>
-        </is>
-      </c>
+          <t>Bolalar xavfsizlik pardachalari bilan jihozlangan 16A rozetka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1043,34 +979,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WK 6515B  — прецизионный ВЧ измеритель</t>
+          <t>TESS 2-talik blok rozetka (oq)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>35 000 so'm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/18/2024-10-18-16-24-59-208003-407ce4279beafa7e4ad3b250ee4af976.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/wk-6515b-pretsizionniy-vch-izmeritel-1047370/</t>
-        </is>
-      </c>
+          <t>Yagona korpusdagi ikkitalik yerga ulangan rozetka, 16A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1078,34 +1010,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WK 6505B — прецизионный ВЧ измеритель</t>
+          <t>TESS Podrozetnik gipsokarton va g'isht devor uchun</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>TESS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>3 500 so'm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-15-49-01-142835-3b145f958583d282a4f20c05bded8a05.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/wk-6505b-pretsizionniy-vch-izmeritel-1057125/</t>
-        </is>
-      </c>
+          <t>O'chirgich va rozetkalarni devorga o'rnatish uchun plastik montaj qutisi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1113,34 +1041,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>testo 511 - Манометр абсолютного давления серии "Pocket Line"</t>
+          <t>Nilson Touran 1-klavishli o'chirgich (oq)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Testo</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2 000 000 so'm</t>
+          <t>24 000 so'm</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/18/2023-12-18-20-53-25-629312-705f34c00be85169662c598c5774c48a.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/testo-511-manometr-absolyutnogo-davleniya-serii-pocket-line-919653/</t>
-        </is>
-      </c>
+          <t>Turkiya sifati, olovga chidamli polikarbonat korpus, 10A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1148,34 +1072,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RGK AZ-40 — угломер</t>
+          <t>Nilson Touran Yerga ulangan rozetka (krem)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>26 000 so'm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-14-43-18-255075-7872beaa7df7783d9c139075cad28bba.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-az-40-uglomer-1055950/</t>
-        </is>
-      </c>
+          <t>Klassik krem rangi, zanglamas po'lat qisqichli kontaktlar, 16A</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1183,34 +1103,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNI-T LM600G — лазерный дальномер</t>
+          <t>Nilson Thor Tashqi rozetka IP54 (namlikdan himoyalangan)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNI-T</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>38 000 so'm</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-08-08-12-617626-52da607d66d0ba312853eaf239f423a0.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/uni-t-lm600g-lazerniy-dalnomer-1060444/</t>
-        </is>
-      </c>
+          <t>Ko'cha, garaj va nam xonalar uchun qopqoqli tashqi montaj rozetkasi</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1218,34 +1134,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UNI-T UT582+ — тестер УЗО цифровой</t>
+          <t>Nilson Touran Ramka 3-talik gorizontal (oq)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNI-T</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NILSON</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>16 000 so'm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/17/2024-03-17-20-34-59-468071-a721681b76abd98459b022058ba0ee69.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/uni-t-ut582-tester-uzo-tsifrovoy-955911/</t>
-        </is>
-      </c>
+          <t>Uchta modulni birlashtirish uchun dekorativ bezak ramkasi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1253,34 +1165,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MDR-40-5 блок питания на DIN</t>
+          <t>Oydin Electric 60x60 LED panel 48W 6500K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>95 000 so'm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-10-18-02-990085-8c1a5277ecb44162ca564c0ceb9ad879.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/mdr-40-5-blok-pitaniya-na-din-931950/</t>
-        </is>
-      </c>
+          <t>Ofis va savdo markazlari Armstrong shiftlari uchun yorqin va tejamkor panel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1288,34 +1196,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>testo 470 - Тахометр</t>
+          <t>Oydin Electric Dumaloq LED svetilnik 18W oq</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Testo</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>32 000 so'm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/19/2023-12-19-10-22-39-434961-c3d65eaf9aefa770d8a655f412f7921b.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/testo-470-taxometr-919745/</t>
-        </is>
-      </c>
+          <t>Shiftga o'rnatiluvchi ingichka LED panel, 1400 lumen, 6000K</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1323,34 +1227,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ЧЭП3601 — устройство размагничивания трансформаторов</t>
+          <t>Oydin Electric LED projektor 50W IP65 (ko'cha uchun)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>85 000 so'm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-02-04-29-338525-0749817a1316620bd9e4373a7eeba3f9.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/chep3601-ustroystvo-razmagnichivaniya-transformatorov-1062217/</t>
-        </is>
-      </c>
+          <t>Suv va chang o'tkazmaydigan alyuminiy korpusli tashqi yoritish projektori</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1358,34 +1258,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RGK R-50 — рулетка</t>
+          <t>Oydin Electric Toshli LED lampa E27 15W 6500K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>12 000 so'm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-02-19-05-744901-0440d4aaa5ef25d929359e9599d52715.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-r-50-ruletka-1056898/</t>
-        </is>
-      </c>
+          <t>Kunduzgi oq yorug'lik beruvchi yuqori sifatli tejamkor LED lampochka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1393,34 +1289,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ЛАЗЕРНЫЙ ДАЛЬНОМЕР FLUKE 414D</t>
+          <t>Oydin Electric LED lenta 2835 12V 120 led/m (oq)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>OYDIN ELECTRIC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1 000 so'm</t>
+          <t>15 000 so'm</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/27/2023-12-27-10-56-46-064015-5e86a9b5aa416bc95fb251f46cd79ebd.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/lazerniy-dalnomer-fluke-414d-928202/</t>
-        </is>
-      </c>
+          <t>Yashirin va dekorativ yoritish uchun 1 metr narxi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1428,32 +1320,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MS6013 — цифровой измеритель емкости</t>
+          <t>Предохранитель ПКЭ 106-6-20-40 У2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>10 000 so'm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/05/2025-01-05-15-42-00-520398-40c97bef5eec7b325deea9d22de5809e.webp?_=ozauc</t>
+          <t>Предохранитель ПКЭ 106-6-20-40 У2 - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/ms6013-tsifrovoy-izmeritel-emkosti-1071861/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-17-39-00-501839-01fbe1afb9239861a6460e94fe7d8dd1.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -1463,34 +1355,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ЛАТР 1.25 — автотрансформатор</t>
+          <t>Nura Electric Avtomat o'chirgich 1P 16A 4.5kA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>19 000 so'm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/14/2024-09-14-16-08-18-358020-c312e688d62cfafd40c9a10ace131917.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/latr-125-avtotransformator-1037006/</t>
-        </is>
-      </c>
+          <t>Xonadon va ofis rozetkalari zanjirini ortiqcha yuklama va qisqa tutashuvdan himoya qilish</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1498,34 +1386,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PA194I-9xxx — амперметр переменного тока</t>
+          <t>Nura Electric Avtomat o'chirgich 1P 25A 4.5kA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>20 000 so'm</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/18/2024-03-18-19-52-41-563658-6cccdb1d1163b1bc5ff00f12df28479b.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/pa194i-9xxx-ampermetr-peremennogo-toka-956305/</t>
-        </is>
-      </c>
+          <t>Konditsioner va oshxona maishiy texnikalari uchun himoya avtomati</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1533,34 +1417,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WK 6550B — прецизионный ВЧ измеритель</t>
+          <t>Nura Electric Avtomat o'chirgich 3P 40A 6kA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>65 000 so'm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/18/2024-10-18-16-59-00-904659-ce0ff0d3d70e2b498176fe3f6d188bfe.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/wk-6550b-pretsizionniy-vch-izmeritel-1047387/</t>
-        </is>
-      </c>
+          <t>Uch fazali kirish tarmoqlari va quvvatli uskunalar uchun avtomat</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1568,34 +1448,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DCM2000DR — токовые клещи True RMS</t>
+          <t>Nura Electric Taqsimlash qutisi (raspaedkorobka) 100x100 IP55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>NURA ELECTRIC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>14 000 so'm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/08/2024-11-08-22-13-27-483440-e04b177905781ccf329925e3f04a30e3.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/dcm2000dr-tokovie-kleshi-true-rms-1054212/</t>
-        </is>
-      </c>
+          <t>Kabellarni ulash va tarmoqlash uchun tashqi germetik quti</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1603,32 +1479,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MY-64 — мультиметр</t>
+          <t>MDR-40-5 блок питания на DIN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>Kelishilgan holda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/06/2025-01-06-13-33-16-577320-43cfe54e298934f50fd87dd9ff748e4f.webp?_=ozauc</t>
+          <t>MDR-40-5 блок питания на DIN - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/my-64-multimetr-1072172/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-10-18-02-990085-8c1a5277ecb44162ca564c0ceb9ad879.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -1638,34 +1514,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DT-351 Клещи электроизмерительные</t>
+          <t>CHINT NXB-63 Avtomat o'chirgich 1P 16A 6kA C-tipli</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10 000 so'm</t>
+          <t>24 000 so'm</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-20-27-12-149015-13c42446845d2dd40635231298cbe51e.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/dt-351-kleshi-elektroizmeritelnie-932048/</t>
-        </is>
-      </c>
+          <t>Sanoat va maishiy tarmoqlar uchun yuqori ishonchli modular avtomat o'chirgich</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1673,34 +1545,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RGK DL100 — оптический дальномер с угломером</t>
+          <t>CHINT NXB-63 Avtomat o'chirgich 3P 25A 6kA C-tipli</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>72 000 so'm</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-01-00-51-699611-717edc7bf2729e558167de55cd995510.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-dl100-opticheskiy-dalnomer-s-uglomerom-1054377/</t>
-        </is>
-      </c>
+          <t>Uch fazali yuklamalar va motorlar uchun 3 qutbli avtomat o'chirgich</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1708,34 +1576,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>АКИП-5104/2 — частотомер</t>
+          <t>CHINT NXB-63 Avtomat o'chirgich 3P 63A 6kA C-tipli</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>АКИП</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>88 000 so'm</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/12/2024-09-12-11-03-11-026117-cc7023ea2e3abd2334b95cfb3ee63aeb.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/akip-51042-chastotomer-1036112/</t>
-        </is>
-      </c>
+          <t>Kirish qismi va kuchli yuklamalar uchun sifatli avtomat</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1743,34 +1607,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Измеритель прочности бетона ИПС-МГ4.03</t>
+          <t>CHINT NL1-63 Differensial rele (UZO) 2P 25A 30mA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26 990 000 so'm</t>
+          <t>145 000 so'm</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/proposals/2025/04/07/2025-04-07-17-13-49-405982-c5eb1f2339c5f1ffc45675f4ed8659a5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/izmeritel-prochnosti-betona-ips-mg403-1091954/</t>
-        </is>
-      </c>
+          <t>Insonni elektr toki urishidan va yong'indan himoya qiluvchi xavfsizlik o'chirgichi</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1778,34 +1638,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MSO2302A-S — цифровой осциллограф</t>
+          <t>CHINT NXC-25 Magnit kontaktor 25A 220V 1NO+1NC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>125 000 so'm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-21-38-21-704488-ce1fae3d4d9fb3489b1acc59ca42ec11.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/mso2302a-s-tsifrovoy-ostsillograf-1060673/</t>
-        </is>
-      </c>
+          <t>Elektr dvigatellari va quvvat zanjirlarini masofadan boshqarish va ishga tushirish uchun</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1813,34 +1669,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ТЕПЛОВИЗОР FLUKE TI400</t>
+          <t>CHINT RT28-32 Silindrsimon saqlagich ushlagichi va vstavkasi 10x38 16A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>CHINT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>15 000 so'm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-00-15-527210-0a6393d10bd41b68f9972032fdcb8a7f.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/teplovizor-fluke-ti400-923356/</t>
-        </is>
-      </c>
+          <t>DIN-reykaga o'rnatiluvchi tezkor eriydigan saqlagich bloki</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1848,34 +1700,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ТЕПЛОВИЗОР FLUKE TIS55</t>
+          <t>Baumann Electric Avtomat o'chirgich 1P 16A 4.5kA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>17 000 so'm</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-20-33-35-032534-b028ea37041e91661b76843d57df5a58.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/teplovizor-fluke-tis55-923305/</t>
-        </is>
-      </c>
+          <t>Zamonaviy standartlar bo'yicha ishlab chiqarilgan himoya avtomati</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1883,34 +1731,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PQ215 — регистратор температуры</t>
+          <t>Baumann Electric Avtomat o'chirgich 3P 32A 6kA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>56 000 so'm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-01-02-35-181761-a007e45959ced436144319a47b30ffc5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/pq215-registrator-temperaturi-1060375/</t>
-        </is>
-      </c>
+          <t>Bino ichki tarmoqlarini xavfsiz boshqarish uchun 3 fazali o'chirgich</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1918,34 +1762,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RGK D600-A — оптический дальномер</t>
+          <t>Baumann Electric Kuchlanish nazorati relesi 40A 220V</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>135 000 so'm</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-23-01-26-643836-293b6a22bb5e7c265a8ae3ed59287480.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-d600-a-opticheskiy-dalnomer-1057807/</t>
-        </is>
-      </c>
+          <t>Tarmoqdagi kuchlanish sakrashlaridan maishiy texnikalarni himoyalovchi raqamli rele</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1953,34 +1793,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AT-8 Цифровой лазерный фототахометр, контактно-бесконтактный</t>
+          <t>Baumann PVX Izolyatsiya tasmasi (izolenta) 19mm x 20m qora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>BAUMANN ELECTRIC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1 865 000 so'm</t>
+          <t>6 000 so'm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/25/2024-01-25-16-17-38-595327-430b69cb37b245b3b8bbdb3667ea6868.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/at-8-tsifrovoy-lazerniy-fototaxometr-kontaktno-beskontaktniy-941687/</t>
-        </is>
-      </c>
+          <t>Elektr simlarini professional izolyatsiyalash uchun chidamli lenta</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1988,34 +1824,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NA520 — оптический нивелир</t>
+          <t>ProCab VVGng-LS 3x1.5 Mis quvvat kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>8 500 so'm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-14-45-39-458593-f3d0f53621a7cf2290e27369bc4a98b5.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/na520-opticheskiy-nivelir-1061548/</t>
-        </is>
-      </c>
+          <t>Yoritish tizimlari uchun yonmaydigan, kam tutunli sifatli mis kabel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2023,34 +1855,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RGK T-20 — электронный теодолит</t>
+          <t>ProCab VVGng-LS 3x2.5 Mis quvvat kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>13 800 so'm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-13-34-17-348049-9e191adbb7cc26a98996fd6facf5f8cb.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-t-20-elektronniy-teodolit-1055856/</t>
-        </is>
-      </c>
+          <t>Rozetkalar va bino ichki simlari uchun standart quvvatli mis kabel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2058,34 +1886,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>АКИП-8407/1 — измеритель параметров электрических сетей</t>
+          <t>ProCab VVGng-LS 3x4 Mis quvvat kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>АКИП</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>21 500 so'm</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/12/2024-09-12-13-25-02-960042-22a42eb547b2241b0ba0b6a38a955f4b.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/akip-84071-izmeritel-parametrov-elektricheskix-setey-1036178/</t>
-        </is>
-      </c>
+          <t>Plitalar, suv isitgichlar va kuchli yuklamalar uchun mis kabel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2093,34 +1917,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RGK PR-81G — лазерный уровень</t>
+          <t>ProCab AVVG 4x16 Alyuminiy kirish kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>19 000 so'm</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-12-43-33-819144-605ca97aea33c5078ea22073bada9538.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-pr-81g-lazerniy-uroven-1054422/</t>
-        </is>
-      </c>
+          <t>Yer osti va havo orqali uyga kirish tarmoqlari uchun 4 tomirli alyuminiy kabel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2128,34 +1948,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>АКИП-3418/1 — генератор сигналов произвольной формы</t>
+          <t>ProCab PVS 2x1.5 Egiluvchan shnur (1 metr)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>АКИП</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>PROCAB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11 160 000 so'm</t>
+          <t>6 200 so'm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/29/2024-05-29-09-43-27-594636-a6b3b8ec4b841fc890accf25f9ebc33e.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/akip-34181-generator-signalov-proizvolnoy-formi-1000220/</t>
-        </is>
-      </c>
+          <t>Maishiy texnika va uzaytirgichlar uchun juda qulay egiluvchan shnur</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2163,34 +1979,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SSU5264A — переключатель ВЧ сигналов механический</t>
+          <t>Uzkabel VVGng 3x1.5 Mis montaj kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>8 200 so'm</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-17-39-45-945454-ce0875bc036a0f13ec79cd8fb33b18ad.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/ssu5264a-pereklyuchatel-vch-signalov-mexanicheskiy-1062714/</t>
-        </is>
-      </c>
+          <t>Davlat standarti (GOST) bo'yicha toza misdan tayyorlangan olovga chidamli kabel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2198,34 +2010,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Метерон ИСП-80 — испытательная установка СНЧ</t>
+          <t>Uzkabel VVGng 3x2.5 Mis montaj kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>13 500 so'm</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/06/2024-02-06-20-26-26-815794-9b062c109ae0154864525af230151c7e.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/meteron-isp-80-ispitatelnaya-ustanovka-snch-945761/</t>
-        </is>
-      </c>
+          <t>GOST standartidagi ishonchli rozetka zanjirlari kabeli</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2233,34 +2041,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Константа ВЗ-4 — вискозиметр</t>
+          <t>Uzkabel VVGng 3x4 Mis montaj kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>21 000 so'm</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/04/2024-05-04-13-50-57-126103-bd450f4c6151d536b0f9aec68f4a5eef.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/konstanta-vz-4-viskozimetr-993482/</t>
-        </is>
-      </c>
+          <t>Kuchli elektr jihozlari va tarqatish shiti magistrallari uchun</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2268,34 +2072,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Elitech VGW-mini — беспроводной цифровой вакуумметр</t>
+          <t>Uzkabel SIP-4 4x16 Havo elektr tarmog'i kabeli (1 metr)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Пирометры</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>24 000 so'm</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/04/2024-11-04-00-50-25-194172-75212f342a89819f388f790b7c0c0ad1.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/elitech-vgw-mini-besprovodnoy-tsifrovoy-vakuummetr-1052379/</t>
-        </is>
-      </c>
+          <t>Ustundan uyga elektr tortish uchun o'z-o'zini tutuvchi izolyatsiyalangan kabel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2303,34 +2103,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SEM5004A (020) — модуль электронной калибровки</t>
+          <t>Uzkabel APV 16 Alyuminiy montaj o'tkazgichi (1 metr)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>UZKABEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>3 500 so'm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/29/2024-11-29-22-14-34-903802-bbfdc36e521f135ec7f0bda01ede1474.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/sem5004a-020-modul-elektronnoy-kalibrovki-1063278/</t>
-        </is>
-      </c>
+          <t>Yagona tomirli alyuminiy sim quvurlarda montaj qilish uchun</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2338,34 +2134,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Лис-М+ — поисковый комплект</t>
+          <t>Gofra truba PVX d=16 mm zondli olovga chidamli (100 m)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>110 000 so'm</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/23/2024-04-23-20-37-35-029470-fc3651abe79d2b2c793e5c74ce872861.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/lis-m-poiskoviy-komplekt-967798/</t>
-        </is>
-      </c>
+          <t>Yoritish kabellarini devor ichida va gipsokarton orqasida xavfsiz o'tkazish uchun</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2373,34 +2165,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>vLocDM2 — трассоискатель</t>
+          <t>Gofra truba PVX d=20 mm zondli olovga chidamli (100 m)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>140 000 so'm</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-14-11-57-032088-c8d425f0b404f34045efb1556fd0f68f.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/vlocdm2-trassoiskatel-1057066/</t>
-        </is>
-      </c>
+          <t>Rozetka kabellari uchun eng ommabop po'lat zondli gofra shlang</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2408,34 +2196,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mastech M266C — токоизмерительные клещи</t>
+          <t>Gofra truba PVX d=25 mm zondli olovga chidamli (50 m)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mastech</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>95 000 so'm</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/04/2025-01-04-20-54-13-089934-ff3aa0eadc8e78d8c32337fde9c13ae7.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/mastech-m266c-tokoizmeritelnie-kleshi-1071640/</t>
-        </is>
-      </c>
+          <t>Qalin kabellar va bir nechta simlarni birga tortish uchun gofra truba</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2443,34 +2227,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RM-104 — измеритель пульсаций</t>
+          <t>Metallangandosh shlang (metallogofra) d=20 mm (50 m)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>180 000 so'm</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/23/2024-10-23-17-51-42-923752-6d446e3e2d839ca326193c8b843753dd.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rm-104-izmeritel-pulsatsiy-1048897/</t>
-        </is>
-      </c>
+          <t>Kabellarni mexanik shikastlanishdan va kemiruvchilardan himoyalovchi metall shlang</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2478,34 +2258,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX500</t>
+          <t>Kabel kanal (korob) 25x16 mm oq 2 metr</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>9 500 so'm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-19-49-935600-ed70c1a6e3287dd6f999f0b4ab8ab3ac.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/infrakrasnaya-kamera-fluke-tix500-923367/</t>
-        </is>
-      </c>
+          <t>Ochiq simlarni devor bo'ylab estetik va xavfsiz yotqizish uchun plastik korob</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2513,34 +2289,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RGK RT-30 — мегаомметр</t>
+          <t>Kabel kanal (korob) 40x25 mm oq 2 metr</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>16 000 so'm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-13-16-30-536285-dc0d466eec61958b1c368e6aaeb4a38e.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-rt-30-megaommetr-1055837/</t>
-        </is>
-      </c>
+          <t>Katta hajmli kabellar to'plami uchun qopqoqli kabel kanali</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2548,34 +2320,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RGK U3060 — пузырьковый уровень</t>
+          <t>Kabel kanal (korob) 60x40 mm oq 2 metr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>gofra va korp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>28 000 so'm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-12-31-34-951072-8c66f92b0ad482e1eac2c646f3f3596e.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-u3060-puzirkoviy-uroven-1057379/</t>
-        </is>
-      </c>
+          <t>Magistral kabellarni yotqizish uchun keng profilli korob</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2583,32 +2351,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SNOL 7,2/900 с интерфейсным терморегулятором — электропечь</t>
+          <t>ИПП120 информационная программируемая панель оператора</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Metall shitlar</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Инфракрасные термометры</t>
-        </is>
-      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>1 900 000 so'm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-00-23-38-649017-0137afcb2400659f225136666d6021f9.webp?_=ozauc</t>
+          <t>ИПП120 информационная программируемая панель оператора - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/snol-72900-s-interfeysnim-termoregulyatorom-elektropech-1061386/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/10/2024-01-10-09-38-17-877959-ca1c55524f08794078f77211f1b7e1e5.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -2618,34 +2386,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ПР-3366 — клещи электроизмерительные</t>
+          <t>ShVR-12 Metall taqsimlash shiti (ichki o'rnatish) IP31</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>120 000 so'm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-19-54-40-650709-47ffc510d34ae0150111773e826180ec.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/pr-3366-kleshi-elektroizmeritelnie-1057223/</t>
-        </is>
-      </c>
+          <t>12 ta modular avtomat uchun devor ichiga o'rnatiladigan po'lat korpusli shit</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2653,34 +2417,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RGK PR-3R — лазерный построитель плоскостей</t>
+          <t>ShVR-24 Metall taqsimlash shiti (ichki o'rnatish) IP31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>165 000 so'm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-02-48-06-360607-03b6927eb35cd1022e85f0f4af1682eb.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-pr-3r-lazerniy-postroitel-ploskostey-1054395/</t>
-        </is>
-      </c>
+          <t>24 ta modular avtomat uchun 2 qatorli qulfli metall shit</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2688,34 +2448,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trotec BS30WP appSensor — шумомер</t>
+          <t>ShRN-24 Metall taqsimlash shiti (tashqi montaj) IP31</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Trotec</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>175 000 so'm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/12/24/2024-12-24-22-53-45-535873-ba25528e13e21bd84619cc33adbf8d24.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/trotec-bs30wp-appsensor-shumomer-1069985/</t>
-        </is>
-      </c>
+          <t>Devor ustiga o'rnatiladigan 24 modulli changdan himoyalangan po'lat shit</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2723,34 +2479,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TR220 — измеритель шероховатости</t>
+          <t>ShRN-36 Metall taqsimlash shiti (tashqi montaj) IP54</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>240 000 so'm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/12/2024-11-12-00-50-04-346442-0c87a170883b815c6ec3787954c49a0c.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/tr220-izmeritel-sheroxovatosti-1055040/</t>
-        </is>
-      </c>
+          <t>Namlik va changdan himoyalangan 36 modulli ko'cha va sex shiti</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2758,34 +2510,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>М419 — омметр</t>
+          <t>ShchMP-1 Metall montaj panelli shkaf (395x310x220) IP54</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kelishilgan holda</t>
+          <t>210 000 so'm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/08/2024-02-08-21-44-25-960649-31f10651aa55214e6c9a015779921d80.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/m419-ommetr-946405/</t>
-        </is>
-      </c>
+          <t>Avtomatika, rele va apparaturalar o'rnatish uchun yechiladigan panelli shkaf</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2793,34 +2541,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RGK U7080 — пузырьковый уровень</t>
+          <t>ShchUR-1F/3F Elektr hisoblagich uchun metall shit qulfli</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Metall shitlar</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Brendsiz</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>185 000 so'm</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/14/2024-11-14-23-56-05-528387-e0bdb1f5a7f68c2a529718e055ce0aa0.webp?_=ozauc</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-u7080-puzirkoviy-uroven-1056834/</t>
-        </is>
-      </c>
+          <t>1 yoki 3 fazali hisoblagich va kirish avtomatlari uchun oynali metall quti</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2828,32 +2572,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DS1102Z-E — цифровой осциллограф</t>
+          <t>ПИРОМЕТР ИНФРАКРАСНЫЙ FLUKE 568</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>10 000 so'm</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/24/2024-11-24-00-06-11-138207-a1499f072ea67071341be2c84c7726bd.webp?_=ozauc</t>
+          <t>ПИРОМЕТР ИНФРАКРАСНЫЙ FLUKE 568 - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/ds1102z-e-tsifrovoy-ostsillograf-1060769/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/29/2023-12-29-21-38-31-701803-ddb6387de8ffe41da55f05be32d1951c.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -2863,32 +2607,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Комплект testo 400 для вентиляции с зондом-крыльчаткой 16 мм</t>
+          <t>IR-67 Инфракрасный термометр (пирометр)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Testo</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>Kelishilgan holda</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/18/2023-12-18-17-47-33-967849-1d6fa18aa547d424d554efd415f54f75.webp?_=ozauc</t>
+          <t>IR-67 Инфракрасный термометр (пирометр) - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/komplekt-testo-400-dlya-ventilyatsii-s-zondom-krilchatkoy-16-mm-919601/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/03/2024-01-03-21-22-53-534917-418ad2bcf113f41bf7537bbda28bff97.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -2898,32 +2642,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DS1054Z — цифровой осциллограф</t>
+          <t>Кельвин Компакт 600 (К46) — ИК-термометр</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Инфракрасные термометры</t>
-        </is>
-      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>6 525 000 so'm</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-16-10-28-801077-e2ec19ced4ea3129cd511d41164291ac.webp?_=ozauc</t>
+          <t>Кельвин Компакт 600 (К46) — ИК-термометр - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/ds1054z-tsifrovoy-ostsillograf-1060618/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/02/2024-02-02-12-01-23-286401-fad8dd6f46759895ca8c19ddf269e562.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -2933,32 +2677,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Предохранитель ПКЭ 106-6-20-40 У2</t>
+          <t>Victor 6056A+ AC/DC — токовые клещи</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10 000 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-17-39-00-501839-01fbe1afb9239861a6460e94fe7d8dd1.webp?_=ozauc</t>
+          <t>Victor 6056A+ AC/DC — токовые клещи - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/predoxranitel-pke-106-6-20-40-u2-932023/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/20/2024-10-20-11-01-29-676911-16e5bfb1b3d4a8b6a589bb6880846e73.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -2968,17 +2712,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UNI-T UT136C+ — мультиметр цифровой портативный</t>
+          <t>Michell S8000 — прецизионный гигрометр с охлаждаемым зеркалом</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UNI-T</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Michell</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2988,12 +2732,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/20/2024-11-20-18-50-05-718189-c1f42cf9092d48eed064dd980137bdfd.webp?_=ozauc</t>
+          <t>Michell S8000 — прецизионный гигрометр с охлаждаемым зеркалом - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/uni-t-ut136c-multimetr-tsifrovoy-portativniy-1059171/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/29/2024-11-29-23-31-36-418915-6de0e2a7ad2e1f5d9e328164f6141ad2.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3003,32 +2747,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 303</t>
+          <t>DT-355 Клещи электроизмерительные, True RMS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>Kelishilgan holda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/16/2024-09-16-11-44-25-503807-6429798907511ca3228fd80d851ba514.webp?_=ozauc</t>
+          <t>DT-355 Клещи электроизмерительные, True RMS - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tokoizmeritelnie-kleshi-fluke-303-1037318/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/01/2024-01-01-22-00-17-631902-0ffb047bad84684a2d3d25002e0620a5.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3038,32 +2782,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RGK GM-2D-B — бипод для геодезической рейки широкой 7,5 - 9 см</t>
+          <t>RIGOL DHO1102— цифровой осциллограф</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>15 000 000 so'm</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-11-36-53-640270-46ae6c59ea1bb689d02196d266c1b970.webp?_=ozauc</t>
+          <t>RIGOL DHO1102— цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/rgk-gm-2d-b-bipod-dlya-geodezicheskoy-reyki-shirokoy-75-9-sm-1055757/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/20/2024-01-20-10-37-51-508421-b43710421f7d3b9ebf2d93ddf49180c5.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3073,32 +2817,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAT HotFind-S — тепловизор</t>
+          <t>Взрывозащищенный датчик давления ATM/Ex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Инфракрасные термометры</t>
-        </is>
-      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/07/2024-11-07-22-28-15-794178-a6c9368edddc5f394a3eb241fdc4ad2e.webp?_=ozauc</t>
+          <t>Взрывозащищенный датчик давления ATM/Ex - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/sat-hotfind-s-teplovizor-1053825/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/06/2024-05-06-22-45-30-468613-4ba6ca29e4ec8de53e7414192fd2e338.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3108,32 +2852,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ТЕСТЕР FLUKE NETWORKS MICROMAPPER MT-8200-49A</t>
+          <t>SLS-720F классик (Ду 25 мм) — стационарный ультразвуковой расходомер</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>Kelishilgan holda</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/24/2023-12-24-14-24-17-463751-9cc08e847ddb564e8fff3d75dd389d61.webp?_=ozauc</t>
+          <t>SLS-720F классик (Ду 25 мм) — стационарный ультразвуковой расходомер - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tester-fluke-networks-micromapper-mt-8200-49a-924263/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/31/2023-12-31-10-41-30-517529-c5a019e8e1c6032a8b67875961317539.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3143,32 +2887,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ТЕСТЕР FLUKE T5-600</t>
+          <t>GDM-8245 — вольтметр универсальный цифровой</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>7 000 000 so'm</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/23/2023-12-23-16-12-08-174302-0d0919bfb7b63506501bcfea368d3bb5.webp?_=ozauc</t>
+          <t>GDM-8245 — вольтметр универсальный цифровой - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tester-fluke-t5-600-923905/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/16/2024-01-16-20-57-24-460934-8d506e427d6cc2aca0699a8a0ba3ecc3.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3178,17 +2922,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 355</t>
+          <t>Elitech V700 — вакуумный насос</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3198,12 +2942,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/17/2024-09-17-15-36-18-171469-d9ef1384e0e78c873def180db00213e1.webp?_=ozauc</t>
+          <t>Elitech V700 — вакуумный насос - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tokoizmeritelnie-kleshi-fluke-355-1037916/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/03/2024-11-03-23-30-22-326513-a2097f080f2a4efdc8b08179e4e25bb5.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3213,32 +2957,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RGK GB7 — башмак геодезический</t>
+          <t>HT108L — мультиметр цифровой</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Инфракрасные термометры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/21/2024-11-21-12-40-09-338769-8c7aed46ce8a40f8b55b98dc64d170b0.webp?_=ozauc</t>
+          <t>HT108L — мультиметр цифровой - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/rgk-gb7-bashmak-geodezicheskiy-1059346/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/14/2024-09-14-10-27-54-964996-85dbca89bab5bd412a10089db7256130.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3248,32 +2992,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ТЕПЛОВИЗОР FLUKE TIS20+</t>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЙ ДАТЧИК FLUKE 376</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>Fluke</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/21/2023-12-21-23-09-00-956554-2d2fa5014f8e274dbb1ba8a857d6eb5f.webp?_=ozauc</t>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЙ ДАТЧИК FLUKE 376 - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/teplovizor-fluke-tis20-922658/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/17/2024-09-17-15-46-43-441306-ec99a83afc87c79d0ca8b1f26becb2f4.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3283,32 +3027,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX560</t>
+          <t>PD194PQ-7R0T-A-0001 — многофункциональный цифровой электроизмерительный прибор</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-24-52-384802-1b5e62841a0cc72d351152107ae35b3e.webp?_=ozauc</t>
+          <t>PD194PQ-7R0T-A-0001 — многофункциональный цифровой электроизмерительный прибор - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/infrakrasnaya-kamera-fluke-tix560-923370/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/23/2024-04-23-13-19-10-433871-ccf4e9bc939a1504a9236045ad28af6d.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3318,32 +3062,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ТЕСТЕР ЭЛЕКТРОУСТАНОВОК FLUKE 6500</t>
+          <t>UNI-T UT383BT — измеритель освещенности (люксметр) mini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>UNI-T</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>10 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/23/2023-12-23-18-20-35-260630-46ed0fdc116b80c26563f3c81f497ff6.webp?_=ozauc</t>
+          <t>UNI-T UT383BT — измеритель освещенности (люксметр) mini - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tester-elektroustanovok-fluke-6500-924022/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/22/2024-11-22-19-35-23-500110-a7d81776762b26bdb2912c649630eb7a.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3353,19 +3097,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VF3 — указатель напряжения</t>
+          <t>MSO5072 — цифровой осциллограф</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>1 000 000 so'm</t>
@@ -3373,12 +3117,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-23-41-03-651894-b8d766ab4c132c1e1e1d17aadb597329.webp?_=ozauc</t>
+          <t>MSO5072 — цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/vf3-ukazatel-napryajeniya-1061641/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-22-48-46-424996-d51a58237e369e1923aa448a4ec26264.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3388,32 +3132,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MD 9240 — токоизмерительные клещи</t>
+          <t>WK 6515B  — прецизионный ВЧ измеритель</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-00-20-53-445842-560307a7826fd668de45ca73a493e600.webp?_=ozauc</t>
+          <t>WK 6515B  — прецизионный ВЧ измеритель - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/md-9240-tokoizmeritelnie-kleshi-1062176/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/18/2024-10-18-16-24-59-208003-407ce4279beafa7e4ad3b250ee4af976.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3423,32 +3167,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SNOL 15/1100 с программируемым терморегулятором — электропечь</t>
+          <t>WK 6505B — прецизионный ВЧ измеритель</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-00-09-50-928238-76dfea13baaeeaddbbddfa2488358d5d.webp?_=ozauc</t>
+          <t>WK 6505B — прецизионный ВЧ измеритель - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/snol-151100-s-programmiruemim-termoregulyatorom-elektropech-1061382/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-15-49-01-142835-3b145f958583d282a4f20c05bded8a05.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3458,32 +3202,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Константа ВЗ-DIN 53211 №4 — вискозиметр</t>
+          <t>testo 511 - Манометр абсолютного давления серии "Pocket Line"</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>Testo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>2 000 000 so'm</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/20/2024-10-20-15-41-38-900899-e5be52e12555c1092844def5b5d04ee1.webp?_=ozauc</t>
+          <t>testo 511 - Манометр абсолютного давления серии "Pocket Line" - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/konstanta-vz-din-53211-no4-viskozimetr-1047897/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/18/2023-12-18-20-53-25-629312-705f34c00be85169662c598c5774c48a.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3493,17 +3237,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quest X10 PRO — металлодетектор</t>
+          <t>RGK AZ-40 — угломер</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>RGK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3513,12 +3257,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/11/2024-11-11-23-17-54-953159-811d33b80f178448cfe8d937ad17c04e.webp?_=ozauc</t>
+          <t>RGK AZ-40 — угломер - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/quest-x10-pro-metallodetektor-1055020/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-14-43-18-255075-7872beaa7df7783d9c139075cad28bba.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3528,17 +3272,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MSO72504DX — цифровой осциллограф</t>
+          <t>UNI-T LM600G — лазерный дальномер</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>UNI-T</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3548,12 +3292,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/03/2025-01-03-18-24-09-287800-9aecc93ff98686642214fa4c4af42d58.webp?_=ozauc</t>
+          <t>UNI-T LM600G — лазерный дальномер - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/mso72504dx-tsifrovoy-ostsillograf-1071294/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-08-08-12-617626-52da607d66d0ba312853eaf239f423a0.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3563,19 +3307,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UNI-T UT803 — мультиметр цифровой настольный универсальный многофункциональный</t>
+          <t>UNI-T UT582+ — тестер УЗО цифровой</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>UNI-T</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>100 000 so'm</t>
@@ -3583,12 +3327,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/26/2024-04-26-09-35-35-737750-b7085d72900284029b9679d8f2f14257.webp?_=ozauc</t>
+          <t>UNI-T UT582+ — тестер УЗО цифровой - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/uni-t-ut803-multimetr-tsifrovoy-nastolniy-universalniy-mnogofunktsionalniy-991049/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/17/2024-03-17-20-34-59-468071-a721681b76abd98459b022058ba0ee69.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3598,32 +3342,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RGK S8-P — штатив</t>
+          <t>testo 470 - Тахометр</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Тепловизоры</t>
+          <t>Testo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>10 so'm</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-00-31-05-468019-ea6a140c1f13b55fb2157dfb1f8533af.webp?_=ozauc</t>
+          <t>testo 470 - Тахометр - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/rgk-s8-p-shtativ-1056854/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/19/2023-12-19-10-22-39-434961-c3d65eaf9aefa770d8a655f412f7921b.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3633,19 +3377,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2260B-30-36 — источник питания</t>
+          <t>ЧЭП3601 — устройство размагничивания трансформаторов</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Тепловизоры</t>
-        </is>
-      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>1 000 000 so'm</t>
@@ -3653,12 +3397,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/08/2025-01-08-20-14-19-034912-12b390a3aeefb1a2be5427a6adb4cdd4.webp?_=ozauc</t>
+          <t>ЧЭП3601 — устройство размагничивания трансформаторов - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/2260b-30-36-istochnik-pitaniya-1073049/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-02-04-29-338525-0749817a1316620bd9e4373a7eeba3f9.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3668,17 +3412,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TDS2024C — осциллограф цифровой запоминающий</t>
+          <t>RGK R-50 — рулетка</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Газанализаторы</t>
+          <t>RGK</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3688,12 +3432,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/10/2024-03-10-14-11-54-509035-2d8fe1e74b6b2106a2dd8325e17a265b.webp?_=ozauc</t>
+          <t>RGK R-50 — рулетка - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tds2024c-ostsillograf-tsifrovoy-zapominayushiy-954173/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-02-19-05-744901-0440d4aaa5ef25d929359e9599d52715.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3703,32 +3447,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SSU5261A — переключатель ВЧ сигналов механический</t>
+          <t>ЛАЗЕРНЫЙ ДАЛЬНОМЕР FLUKE 414D</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boshqa brendlar</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Газанализаторы</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>1 000 so'm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-18-20-43-583960-9f73c505b32c2348a5071cf4c95ca8a0.webp?_=ozauc</t>
+          <t>ЛАЗЕРНЫЙ ДАЛЬНОМЕР FLUKE 414D - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/ssu5261a-pereklyuchatel-vch-signalov-mexanicheskiy-1062768/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/27/2023-12-27-10-56-46-064015-5e86a9b5aa416bc95fb251f46cd79ebd.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3738,32 +3482,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MG1000 — измеритель сопротивления изоляции</t>
+          <t>MS6013 — цифровой измеритель емкости</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Газанализаторы</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>100 000 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/13/2024-09-13-12-04-54-094135-7e77b4548985959ed0db61d6184fe1ef.webp?_=ozauc</t>
+          <t>MS6013 — цифровой измеритель емкости - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/mg1000-izmeritel-soprotivleniya-izolyatsii-1036555/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/05/2025-01-05-15-42-00-520398-40c97bef5eec7b325deea9d22de5809e.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3517,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ИПП120 информационная программируемая панель оператора</t>
+          <t>ЛАТР 1.25 — автотрансформатор</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Газанализаторы</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1 900 000 so'm</t>
+          <t>1 000 000 so'm</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/10/2024-01-10-09-38-17-877959-ca1c55524f08794078f77211f1b7e1e5.webp?_=ozauc</t>
+          <t>ЛАТР 1.25 — автотрансформатор - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/ipp120-informatsionnaya-programmiruemaya-panel-operatora-935690/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/14/2024-09-14-16-08-18-358020-c312e688d62cfafd40c9a10ace131917.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3808,32 +3552,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ТКА-ПКМ (23) — термогигрометр микропроцессорный</t>
+          <t>PA194I-9xxx — амперметр переменного тока</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Газанализаторы</t>
-        </is>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10 000 000 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-12-11-28-170040-66a986e0db4c995774d31b0c16d6b9dc.webp?_=ozauc</t>
+          <t>PA194I-9xxx — амперметр переменного тока - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/tka-pkm-23-termogigrometr-mikroprotsessorniy-1056967/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/18/2024-03-18-19-52-41-563658-6cccdb1d1163b1bc5ff00f12df28479b.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3843,19 +3587,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAT i-384 — тепловизор</t>
+          <t>WK 6550B — прецизионный ВЧ измеритель</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Дымомеры</t>
-        </is>
-      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>1 000 000 so'm</t>
@@ -3863,12 +3607,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/07/2024-11-07-23-54-24-770915-ca9e50ea1b74aaf294ec3fde1f6d40f2.webp?_=ozauc</t>
+          <t>WK 6550B — прецизионный ВЧ измеритель - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/sat-i-384-teplovizor-1053835/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/18/2024-10-18-16-59-00-904659-ce0ff0d3d70e2b498176fe3f6d188bfe.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3878,32 +3622,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MY-68 — мультиметр</t>
+          <t>DCM2000DR — токовые клещи True RMS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>Boshqa brendlar</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Дымомеры</t>
-        </is>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1 000 000 so'm</t>
+          <t>100 000 so'm</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/04/2025-01-04-20-58-31-728851-cf75a9767d0486482b8707ce17895d48.webp?_=ozauc</t>
+          <t>DCM2000DR — токовые клещи True RMS - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/my-68-multimetr-1071641/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/08/2024-11-08-22-13-27-483440-e04b177905781ccf329925e3f04a30e3.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3913,17 +3657,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RGK MD-20 — металлоискатель</t>
+          <t>MY-64 — мультиметр</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RGK</t>
+          <t>Instrumentlar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Паяльное и сварочное оборудование</t>
+          <t>Boshqa brendlar</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3933,12 +3677,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-23-15-00-603257-257d84b2190a35ec2f6beff337d20ad5.webp?_=ozauc</t>
+          <t>MY-64 — мультиметр - Control Pribor do'koni mahsuloti.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://controlpribor.uz/proposal/rgk-md-20-metalloiskatel-1057813/</t>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/06/2025-01-06-13-33-16-577320-43cfe54e298934f50fd87dd9ff748e4f.webp?_=ozauc</t>
         </is>
       </c>
     </row>
@@ -3948,34 +3692,2646 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>DT-351 Клещи электроизмерительные</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>10 000 so'm</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DT-351 Клещи электроизмерительные - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/02/2024-01-02-20-27-12-149015-13c42446845d2dd40635231298cbe51e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RGK DL100 — оптический дальномер с угломером</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>RGK DL100 — оптический дальномер с угломером - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-01-00-51-699611-717edc7bf2729e558167de55cd995510.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>АКИП-5104/2 — частотомер</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>АКИП</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kelishilgan holda</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>АКИП-5104/2 — частотомер - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/12/2024-09-12-11-03-11-026117-cc7023ea2e3abd2334b95cfb3ee63aeb.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Измеритель прочности бетона ИПС-МГ4.03</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>26 990 000 so'm</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Измеритель прочности бетона ИПС-МГ4.03 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/proposals/2025/04/07/2025-04-07-17-13-49-405982-c5eb1f2339c5f1ffc45675f4ed8659a5.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MSO2302A-S — цифровой осциллограф</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>MSO2302A-S — цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-21-38-21-704488-ce1fae3d4d9fb3489b1acc59ca42ec11.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TI400</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TI400 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-00-15-527210-0a6393d10bd41b68f9972032fdcb8a7f.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TIS55</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TIS55 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-20-33-35-032534-b028ea37041e91661b76843d57df5a58.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PQ215 — регистратор температуры</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>PQ215 — регистратор температуры - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-01-02-35-181761-a007e45959ced436144319a47b30ffc5.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RGK D600-A — оптический дальномер</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>RGK D600-A — оптический дальномер - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-23-01-26-643836-293b6a22bb5e7c265a8ae3ed59287480.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AT-8 Цифровой лазерный фототахометр, контактно-бесконтактный</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1 865 000 so'm</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AT-8 Цифровой лазерный фототахометр, контактно-бесконтактный - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/01/25/2024-01-25-16-17-38-595327-430b69cb37b245b3b8bbdb3667ea6868.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NA520 — оптический нивелир</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>NA520 — оптический нивелир - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-14-45-39-458593-f3d0f53621a7cf2290e27369bc4a98b5.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RGK T-20 — электронный теодолит</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>RGK T-20 — электронный теодолит - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-13-34-17-348049-9e191adbb7cc26a98996fd6facf5f8cb.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>АКИП-8407/1 — измеритель параметров электрических сетей</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>АКИП</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Kelishilgan holda</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>АКИП-8407/1 — измеритель параметров электрических сетей - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/12/2024-09-12-13-25-02-960042-22a42eb547b2241b0ba0b6a38a955f4b.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RGK PR-81G — лазерный уровень</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>RGK PR-81G — лазерный уровень - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-12-43-33-819144-605ca97aea33c5078ea22073bada9538.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>АКИП-3418/1 — генератор сигналов произвольной формы</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>АКИП</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>11 160 000 so'm</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>АКИП-3418/1 — генератор сигналов произвольной формы - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/29/2024-05-29-09-43-27-594636-a6b3b8ec4b841fc890accf25f9ebc33e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SSU5264A — переключатель ВЧ сигналов механический</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SSU5264A — переключатель ВЧ сигналов механический - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-17-39-45-945454-ce0875bc036a0f13ec79cd8fb33b18ad.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Метерон ИСП-80 — испытательная установка СНЧ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kelishilgan holda</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Метерон ИСП-80 — испытательная установка СНЧ - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/06/2024-02-06-20-26-26-815794-9b062c109ae0154864525af230151c7e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Константа ВЗ-4 — вискозиметр</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Константа ВЗ-4 — вискозиметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/05/04/2024-05-04-13-50-57-126103-bd450f4c6151d536b0f9aec68f4a5eef.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Elitech VGW-mini — беспроводной цифровой вакуумметр</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Elitech VGW-mini — беспроводной цифровой вакуумметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/04/2024-11-04-00-50-25-194172-75212f342a89819f388f790b7c0c0ad1.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SEM5004A (020) — модуль электронной калибровки</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SEM5004A (020) — модуль электронной калибровки - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/29/2024-11-29-22-14-34-903802-bbfdc36e521f135ec7f0bda01ede1474.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Лис-М+ — поисковый комплект</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Лис-М+ — поисковый комплект - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/23/2024-04-23-20-37-35-029470-fc3651abe79d2b2c793e5c74ce872861.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>vLocDM2 — трассоискатель</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>vLocDM2 — трассоискатель - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-14-11-57-032088-c8d425f0b404f34045efb1556fd0f68f.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Mastech M266C — токоизмерительные клещи</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mastech</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mastech M266C — токоизмерительные клещи - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/04/2025-01-04-20-54-13-089934-ff3aa0eadc8e78d8c32337fde9c13ae7.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RM-104 — измеритель пульсаций</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>RM-104 — измеритель пульсаций - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/23/2024-10-23-17-51-42-923752-6d446e3e2d839ca326193c8b843753dd.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX500</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX500 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-19-49-935600-ed70c1a6e3287dd6f999f0b4ab8ab3ac.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RGK RT-30 — мегаомметр</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>RGK RT-30 — мегаомметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-13-16-30-536285-dc0d466eec61958b1c368e6aaeb4a38e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RGK U3060 — пузырьковый уровень</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>RGK U3060 — пузырьковый уровень - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-12-31-34-951072-8c66f92b0ad482e1eac2c646f3f3596e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SNOL 7,2/900 с интерфейсным терморегулятором — электропечь</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SNOL 7,2/900 с интерфейсным терморегулятором — электропечь - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-00-23-38-649017-0137afcb2400659f225136666d6021f9.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ПР-3366 — клещи электроизмерительные</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ПР-3366 — клещи электроизмерительные - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-19-54-40-650709-47ffc510d34ae0150111773e826180ec.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RGK PR-3R — лазерный построитель плоскостей</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>RGK PR-3R — лазерный построитель плоскостей - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/10/2024-11-10-02-48-06-360607-03b6927eb35cd1022e85f0f4af1682eb.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Trotec BS30WP appSensor — шумомер</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Trotec</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Trotec BS30WP appSensor — шумомер - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/12/24/2024-12-24-22-53-45-535873-ba25528e13e21bd84619cc33adbf8d24.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TR220 — измеритель шероховатости</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>TR220 — измеритель шероховатости - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/12/2024-11-12-00-50-04-346442-0c87a170883b815c6ec3787954c49a0c.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>М419 — омметр</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Kelishilgan holda</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>М419 — омметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/02/08/2024-02-08-21-44-25-960649-31f10651aa55214e6c9a015779921d80.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RGK U7080 — пузырьковый уровень</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>RGK U7080 — пузырьковый уровень - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/14/2024-11-14-23-56-05-528387-e0bdb1f5a7f68c2a529718e055ce0aa0.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DS1102Z-E — цифровой осциллограф</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>DS1102Z-E — цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/24/2024-11-24-00-06-11-138207-a1499f072ea67071341be2c84c7726bd.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Комплект testo 400 для вентиляции с зондом-крыльчаткой 16 мм</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Testo</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Комплект testo 400 для вентиляции с зондом-крыльчаткой 16 мм - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/18/2023-12-18-17-47-33-967849-1d6fa18aa547d424d554efd415f54f75.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DS1054Z — цифровой осциллограф</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>DS1054Z — цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/23/2024-11-23-16-10-28-801077-e2ec19ced4ea3129cd511d41164291ac.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UNI-T UT136C+ — мультиметр цифровой портативный</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>UNI-T</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>UNI-T UT136C+ — мультиметр цифровой портативный - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/20/2024-11-20-18-50-05-718189-c1f42cf9092d48eed064dd980137bdfd.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 303</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 303 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/16/2024-09-16-11-44-25-503807-6429798907511ca3228fd80d851ba514.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RGK GM-2D-B — бипод для геодезической рейки широкой 7,5 - 9 см</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>RGK GM-2D-B — бипод для геодезической рейки широкой 7,5 - 9 см - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/13/2024-11-13-11-36-53-640270-46ae6c59ea1bb689d02196d266c1b970.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SAT HotFind-S — тепловизор</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SAT HotFind-S — тепловизор - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/07/2024-11-07-22-28-15-794178-a6c9368edddc5f394a3eb241fdc4ad2e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР FLUKE NETWORKS MICROMAPPER MT-8200-49A</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР FLUKE NETWORKS MICROMAPPER MT-8200-49A - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/24/2023-12-24-14-24-17-463751-9cc08e847ddb564e8fff3d75dd389d61.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР FLUKE T5-600</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР FLUKE T5-600 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/23/2023-12-23-16-12-08-174302-0d0919bfb7b63506501bcfea368d3bb5.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 355</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ТОКОИЗМЕРИТЕЛЬНЫЕ КЛЕЩИ FLUKE 355 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/17/2024-09-17-15-36-18-171469-d9ef1384e0e78c873def180db00213e1.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RGK GB7 — башмак геодезический</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>RGK GB7 — башмак геодезический - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/21/2024-11-21-12-40-09-338769-8c7aed46ce8a40f8b55b98dc64d170b0.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TIS20+</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ТЕПЛОВИЗОР FLUKE TIS20+ - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/21/2023-12-21-23-09-00-956554-2d2fa5014f8e274dbb1ba8a857d6eb5f.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX560</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ИНФРАКРАСНАЯ КАМЕРА FLUKE TIX560 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/22/2023-12-22-21-24-52-384802-1b5e62841a0cc72d351152107ae35b3e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР ЭЛЕКТРОУСТАНОВОК FLUKE 6500</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>10 so'm</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ТЕСТЕР ЭЛЕКТРОУСТАНОВОК FLUKE 6500 - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2023/12/23/2023-12-23-18-20-35-260630-46ed0fdc116b80c26563f3c81f497ff6.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>VF3 — указатель напряжения</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>VF3 — указатель напряжения - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-23-41-03-651894-b8d766ab4c132c1e1e1d17aadb597329.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MD 9240 — токоизмерительные клещи</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MD 9240 — токоизмерительные клещи - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-00-20-53-445842-560307a7826fd668de45ca73a493e600.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SNOL 15/1100 с программируемым терморегулятором — электропечь</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SNOL 15/1100 с программируемым терморегулятором — электропечь - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/26/2024-11-26-00-09-50-928238-76dfea13baaeeaddbbddfa2488358d5d.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Константа ВЗ-DIN 53211 №4 — вискозиметр</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Константа ВЗ-DIN 53211 №4 — вискозиметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/10/20/2024-10-20-15-41-38-900899-e5be52e12555c1092844def5b5d04ee1.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Quest X10 PRO — металлодетектор</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Quest X10 PRO — металлодетектор - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/11/2024-11-11-23-17-54-953159-811d33b80f178448cfe8d937ad17c04e.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MSO72504DX — цифровой осциллограф</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MSO72504DX — цифровой осциллограф - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/03/2025-01-03-18-24-09-287800-9aecc93ff98686642214fa4c4af42d58.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UNI-T UT803 — мультиметр цифровой настольный универсальный многофункциональный</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>UNI-T</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>UNI-T UT803 — мультиметр цифровой настольный универсальный многофункциональный - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/04/26/2024-04-26-09-35-35-737750-b7085d72900284029b9679d8f2f14257.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>RGK S8-P — штатив</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>RGK S8-P — штатив - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-00-31-05-468019-ea6a140c1f13b55fb2157dfb1f8533af.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2260B-30-36 — источник питания</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2260B-30-36 — источник питания - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/08/2025-01-08-20-14-19-034912-12b390a3aeefb1a2be5427a6adb4cdd4.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TDS2024C — осциллограф цифровой запоминающий</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>TDS2024C — осциллограф цифровой запоминающий - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/03/10/2024-03-10-14-11-54-509035-2d8fe1e74b6b2106a2dd8325e17a265b.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SSU5261A — переключатель ВЧ сигналов механический</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SSU5261A — переключатель ВЧ сигналов механический - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/28/2024-11-28-18-20-43-583960-9f73c505b32c2348a5071cf4c95ca8a0.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MG1000 — измеритель сопротивления изоляции</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>100 000 so'm</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>MG1000 — измеритель сопротивления изоляции - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/09/13/2024-09-13-12-04-54-094135-7e77b4548985959ed0db61d6184fe1ef.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ТКА-ПКМ (23) — термогигрометр микропроцессорный</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>10 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ТКА-ПКМ (23) — термогигрометр микропроцессорный - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-12-11-28-170040-66a986e0db4c995774d31b0c16d6b9dc.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SAT i-384 — тепловизор</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SAT i-384 — тепловизор - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/07/2024-11-07-23-54-24-770915-ca9e50ea1b74aaf294ec3fde1f6d40f2.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MY-68 — мультиметр</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Boshqa brendlar</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>MY-68 — мультиметр - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2025/01/04/2025-01-04-20-58-31-728851-cf75a9767d0486482b8707ce17895d48.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>RGK MD-20 — металлоискатель</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>RGK</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>1 000 000 so'm</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>RGK MD-20 — металлоискатель - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://files.glotr.uz/company/000/035/796/products/2024/11/16/2024-11-16-23-15-00-603257-257d84b2190a35ec2f6beff337d20ad5.webp?_=ozauc</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
           <t>RGK U7200 — пузырьковый уровень</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Instrumentlar</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>RGK</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Анкерные установки</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>1 000 000 so'm</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>RGK U7200 — пузырьковый уровень - Control Pribor do'koni mahsuloti.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://files.glotr.uz/company/000/035/796/products/2024/11/15/2024-11-15-01-43-29-043640-4ddc636c1775a359ee082a12a35083a0.webp?_=ozauc</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://controlpribor.uz/proposal/rgk-u7200-puzirkoviy-uroven-1056889/</t>
-        </is>
-      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SAM Egiluvchan suv shlangi 1/2" Gayka-Gayka 50 sm</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>16 000 so'm</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Zanglamas po'lat o'rimli, ariston va smesitel uchun egiluvchan suv ulanmasi</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SAM Egiluvchan suv shlangi 1/2" Gayka-Gayka 80 sm</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>21 000 so'm</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Uzoq masofali ulanmalar uchun yuqori bosimga chidamli suv shlangi</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SAM Egiluvchan suv shlangi 1/2" Gayka-Shtutser 60 sm</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>19 000 so'm</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Oshxona va vanna smesitellarining tagiga burab ulanadigan maxsus shtutserli shlang</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SAM Dush shlangi zanglamas po'lat 1.5 m</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>28 000 so'm</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ikki qavatli mustahkam o'rimli, burilmaydigan dush shlangi</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SAM Gaz uchun metall to'qimali shlang 1/2" 1.2 m</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>32 000 so'm</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Gaz plitalari va qozonlar uchun sertifikatlangan sariq chiziqli xavfsiz gaz shlangi</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SAM Kir yuvish mashinasi uchun kirish suv shlangi 2.0 m</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SAM shlanglar</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Brendsiz</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>24 000 so'm</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Avtomat kir yuvish mashinalarini sovuq suv tarmog'iga ulash shlangi</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Lezard Mira Yerga ulangan rozetka (oq)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>22 000 so'm</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Turkiya dizayni, sifatli olovga chidamli korpus, 16A 250V</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Lezard Mira 1-klavishli o'chirgich (oq)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>19 000 so'm</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Yorug'likni boshqarish uchun ishonchli kalit, 10A 250V</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Lezard Mira 2-klavishli o'chirgich (oq)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>24 000 so'm</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Lyustra va guruhli chiroqlar uchun ikkitalik o'chirgich</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Lezard Deriy Yerga ulangan rozetka (krem)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>23 000 so'm</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Oshxona va xonalar interyeri uchun nozik krem tusli rozetka</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Lezard Uzaytirgich 3-talik 5 metr yerga ulangan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>58 000 so'm</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>16A 3500W quvvatga mo'ljallangan mustahkam kabel va korpusli uzaytirgich</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Lezard Uzaytirgich 4-talik 3 metr kalitli (oq)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LEZARD</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>62 000 so'm</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Qizil yoritgichli o'chirgich tugmasi va bolalar himoyasi bilan ta'minlangan</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
